--- a/longitudinal/data_processing_elements_longitudinal-ERC.xlsx
+++ b/longitudinal/data_processing_elements_longitudinal-ERC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ca058780ebd4867/ProPASS/ENRICA_validation/longitudinal/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Melchias\Downloads\harmo_longitudinal_ERC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_F25DC773A252ABDACC1048D5819C5A2C5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0115816-C8EE-48BF-BAB6-0BB232D29775}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD77D748-6094-4879-AE90-35CA5C9469FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="345" windowWidth="26370" windowHeight="16695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="727">
   <si>
     <t>index</t>
   </si>
@@ -792,9 +792,6 @@
     <t>IFCC glycosylated hemoglobin (mmol/mol)</t>
   </si>
   <si>
-    <t>round(w19hba1cifcc, digits = 2)</t>
-  </si>
-  <si>
     <t>lab_chol_total</t>
   </si>
   <si>
@@ -810,9 +807,6 @@
     <t>TOTAL CHOLESTEROL (mg/dL)</t>
   </si>
   <si>
-    <t>round(w19colesterol/38.67, digits = 2)</t>
-  </si>
-  <si>
     <t>lab_chol_hdl</t>
   </si>
   <si>
@@ -825,22 +819,13 @@
     <t>HDL CHOLESTEROL (mg/dL)</t>
   </si>
   <si>
-    <t>round(w19colesterolhdl/38.67, digits = 2)</t>
-  </si>
-  <si>
     <t>lab_chol_ldl</t>
   </si>
   <si>
     <t>Low-density lipoprotein (LDL) cholesterol</t>
   </si>
   <si>
-    <t>w19ldl</t>
-  </si>
-  <si>
     <t>CALCULATED LDL (mg/dL)</t>
-  </si>
-  <si>
-    <t>round(w19colesterolldl/38.67, digits = 2)</t>
   </si>
   <si>
     <t>lab_chol_ldl_calculated</t>
@@ -867,12 +852,6 @@
 NA</t>
   </si>
   <si>
-    <t>case_when(
-w19trigliceridos &gt; 400 ~ NA_real_;
-ELSE ~ round((w19colesterol - w19colesterolhdl - (w19trigliceridos/5))/38.67, digits = 2)
-)</t>
-  </si>
-  <si>
     <t>lab_tg</t>
   </si>
   <si>
@@ -883,9 +862,6 @@
   </si>
   <si>
     <t>TRIGLYCERIDES (mg/dL)</t>
-  </si>
-  <si>
-    <t>round(w19trigliceridos/88.57, digits = 2)</t>
   </si>
   <si>
     <t>lab_crp</t>
@@ -1077,13 +1053,7 @@
     <t>Code non-smokers as 0.</t>
   </si>
   <si>
-    <t>w19q23_a</t>
-  </si>
-  <si>
     <t>On average, hoy much do you smoke of: Cigarettes?</t>
-  </si>
-  <si>
-    <t>round(w19p19_1*7, digits = 2)</t>
   </si>
   <si>
     <t>lsb_sleep_duration</t>
@@ -2143,9 +2113,6 @@
     <t>w23p102a</t>
   </si>
   <si>
-    <t>w17p209b</t>
-  </si>
-  <si>
     <t>w23p77</t>
   </si>
   <si>
@@ -2544,6 +2511,33 @@
   </si>
   <si>
     <t>If one or two values are missing from the score, then they can be substituted with the average score of the non-missing items. Questionnaires with more than two missing values should be disregarded.</t>
+  </si>
+  <si>
+    <t>round(w19q23a01*7, digits = 2)</t>
+  </si>
+  <si>
+    <t>w19q23a01</t>
+  </si>
+  <si>
+    <t>round(w19hba1c_2, digits = 2)</t>
+  </si>
+  <si>
+    <t>round(w19col_tot/38.67, digits = 2)</t>
+  </si>
+  <si>
+    <t>round(w19col_hdl/38.67, digits = 2)</t>
+  </si>
+  <si>
+    <t>round(w19triglice/88.57, digits = 2)</t>
+  </si>
+  <si>
+    <t>case_when(
+w19triglice &gt; 400 ~ NA_real_;
+ELSE ~ round((w19col_tot - w19col_hdl - (w19triglice/5))/38.67, digits = 2)
+)</t>
+  </si>
+  <si>
+    <t>only provide calculated LDL</t>
   </si>
 </sst>
 </file>
@@ -3010,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
@@ -4421,7 +4415,7 @@
         <v>169</v>
       </c>
       <c r="Z33" t="s">
-        <v>240</v>
+        <v>721</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -4432,25 +4426,25 @@
         <v>26</v>
       </c>
       <c r="C34" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" t="s">
         <v>241</v>
       </c>
-      <c r="D34" t="s">
-        <v>242</v>
-      </c>
       <c r="E34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F34" t="s">
         <v>112</v>
       </c>
       <c r="G34" t="s">
+        <v>242</v>
+      </c>
+      <c r="M34" t="s">
         <v>243</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>244</v>
-      </c>
-      <c r="N34" t="s">
-        <v>245</v>
       </c>
       <c r="W34" t="s">
         <v>34</v>
@@ -4462,7 +4456,7 @@
         <v>169</v>
       </c>
       <c r="Z34" t="s">
-        <v>246</v>
+        <v>722</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
@@ -4473,25 +4467,25 @@
         <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F35" t="s">
         <v>112</v>
       </c>
       <c r="G35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="N35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W35" t="s">
         <v>34</v>
@@ -4503,7 +4497,7 @@
         <v>169</v>
       </c>
       <c r="Z35" t="s">
-        <v>251</v>
+        <v>723</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
@@ -4514,40 +4508,43 @@
         <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D36" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E36" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F36" t="s">
         <v>112</v>
       </c>
       <c r="G36" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M36" t="s">
-        <v>254</v>
+        <v>41</v>
       </c>
       <c r="N36" t="s">
-        <v>255</v>
+        <v>251</v>
+      </c>
+      <c r="V36" t="s">
+        <v>726</v>
       </c>
       <c r="W36" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="X36" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="Y36" t="s">
-        <v>169</v>
+        <v>88</v>
       </c>
       <c r="Z36" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4555,31 +4552,31 @@
         <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E37" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F37" t="s">
         <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J37" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N37" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="T37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="W37" t="s">
         <v>34</v>
@@ -4591,7 +4588,7 @@
         <v>147</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>263</v>
+        <v>725</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
@@ -4602,25 +4599,25 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D38" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E38" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F38" t="s">
         <v>112</v>
       </c>
       <c r="G38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M38" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="W38" t="s">
         <v>34</v>
@@ -4632,7 +4629,7 @@
         <v>169</v>
       </c>
       <c r="Z38" t="s">
-        <v>268</v>
+        <v>724</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
@@ -4643,25 +4640,25 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E39" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F39" t="s">
         <v>112</v>
       </c>
       <c r="G39" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M39" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N39" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="W39" t="s">
         <v>34</v>
@@ -4673,7 +4670,7 @@
         <v>169</v>
       </c>
       <c r="Z39" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
@@ -4684,25 +4681,25 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D40" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E40" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F40" t="s">
         <v>112</v>
       </c>
       <c r="G40" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J40" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="K40" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M40" t="s">
         <v>41</v>
@@ -4711,7 +4708,7 @@
         <v>88</v>
       </c>
       <c r="X40" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y40" t="s">
         <v>88</v>
@@ -4728,22 +4725,22 @@
         <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E41" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F41" t="s">
         <v>52</v>
       </c>
       <c r="K41" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L41" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M41" t="s">
         <v>41</v>
@@ -4752,7 +4749,7 @@
         <v>88</v>
       </c>
       <c r="X41" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y41" t="s">
         <v>88</v>
@@ -4769,25 +4766,25 @@
         <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E42" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F42" t="s">
         <v>112</v>
       </c>
       <c r="G42" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J42" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="K42" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M42" t="s">
         <v>41</v>
@@ -4796,7 +4793,7 @@
         <v>88</v>
       </c>
       <c r="X42" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y42" t="s">
         <v>88</v>
@@ -4813,25 +4810,25 @@
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D43" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E43" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F43" t="s">
         <v>52</v>
       </c>
       <c r="J43" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="K43" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="L43" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s">
         <v>41</v>
@@ -4840,7 +4837,7 @@
         <v>88</v>
       </c>
       <c r="X43" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y43" t="s">
         <v>88</v>
@@ -4857,19 +4854,19 @@
         <v>26</v>
       </c>
       <c r="C44" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E44" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F44" t="s">
         <v>112</v>
       </c>
       <c r="G44" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M44" t="s">
         <v>41</v>
@@ -4895,25 +4892,25 @@
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E45" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="F45" t="s">
         <v>112</v>
       </c>
       <c r="G45" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J45" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="K45" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M45" t="s">
         <v>41</v>
@@ -4939,28 +4936,28 @@
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E46" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F46" t="s">
         <v>52</v>
       </c>
       <c r="L46" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M46" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="N46" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="T46" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="W46" t="s">
         <v>34</v>
@@ -4972,7 +4969,7 @@
         <v>72</v>
       </c>
       <c r="Z46" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -4983,34 +4980,34 @@
         <v>26</v>
       </c>
       <c r="C47" t="s">
+        <v>301</v>
+      </c>
+      <c r="D47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E47" t="s">
+        <v>302</v>
+      </c>
+      <c r="F47" t="s">
+        <v>52</v>
+      </c>
+      <c r="J47" t="s">
+        <v>303</v>
+      </c>
+      <c r="K47" t="s">
+        <v>304</v>
+      </c>
+      <c r="L47" t="s">
+        <v>305</v>
+      </c>
+      <c r="M47" t="s">
+        <v>306</v>
+      </c>
+      <c r="N47" t="s">
+        <v>307</v>
+      </c>
+      <c r="T47" t="s">
         <v>308</v>
-      </c>
-      <c r="D47" t="s">
-        <v>309</v>
-      </c>
-      <c r="E47" t="s">
-        <v>309</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-      <c r="J47" t="s">
-        <v>310</v>
-      </c>
-      <c r="K47" t="s">
-        <v>311</v>
-      </c>
-      <c r="L47" t="s">
-        <v>312</v>
-      </c>
-      <c r="M47" t="s">
-        <v>313</v>
-      </c>
-      <c r="N47" t="s">
-        <v>314</v>
-      </c>
-      <c r="T47" t="s">
-        <v>315</v>
       </c>
       <c r="W47" t="s">
         <v>34</v>
@@ -5022,7 +5019,7 @@
         <v>72</v>
       </c>
       <c r="Z47" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -5033,31 +5030,31 @@
         <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D48" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E48" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F48" t="s">
         <v>52</v>
       </c>
       <c r="K48" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="L48" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="M48" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="T48" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="W48" t="s">
         <v>34</v>
@@ -5069,7 +5066,7 @@
         <v>72</v>
       </c>
       <c r="Z48" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
@@ -5080,31 +5077,31 @@
         <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D49" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E49" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F49" t="s">
         <v>112</v>
       </c>
       <c r="G49" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J49" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="K49" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="M49" t="s">
-        <v>325</v>
+        <v>720</v>
       </c>
       <c r="N49" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="W49" t="s">
         <v>34</v>
@@ -5116,7 +5113,7 @@
         <v>169</v>
       </c>
       <c r="Z49" t="s">
-        <v>327</v>
+        <v>719</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="30" x14ac:dyDescent="0.25">
@@ -5127,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="C50" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D50" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E50" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="F50" t="s">
         <v>112</v>
@@ -5142,10 +5139,10 @@
         <v>113</v>
       </c>
       <c r="M50" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="N50" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="W50" t="s">
         <v>34</v>
@@ -5157,10 +5154,10 @@
         <v>169</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="AA50" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
@@ -5171,22 +5168,22 @@
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D51" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E51" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F51" t="s">
         <v>52</v>
       </c>
       <c r="J51" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s">
         <v>41</v>
@@ -5201,10 +5198,10 @@
         <v>147</v>
       </c>
       <c r="Z51" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AA51" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
@@ -5215,31 +5212,31 @@
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D52" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E52" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F52" t="s">
         <v>52</v>
       </c>
       <c r="K52" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L52" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="N52" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="T52" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="W52" t="s">
         <v>34</v>
@@ -5251,7 +5248,7 @@
         <v>72</v>
       </c>
       <c r="Z52" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="75" x14ac:dyDescent="0.25">
@@ -5262,28 +5259,28 @@
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="D53" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E53" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F53" t="s">
         <v>52</v>
       </c>
       <c r="J53" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="N53" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="W53" t="s">
         <v>34</v>
@@ -5295,7 +5292,7 @@
         <v>147</v>
       </c>
       <c r="Z53" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
@@ -5306,19 +5303,19 @@
         <v>26</v>
       </c>
       <c r="C54" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D54" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E54" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F54" t="s">
         <v>52</v>
       </c>
       <c r="L54" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s">
         <v>41</v>
@@ -5344,19 +5341,19 @@
         <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D55" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E55" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F55" t="s">
         <v>52</v>
       </c>
       <c r="L55" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M55" t="s">
         <v>41</v>
@@ -5382,25 +5379,25 @@
         <v>26</v>
       </c>
       <c r="C56" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D56" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E56" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F56" t="s">
         <v>52</v>
       </c>
       <c r="L56" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="N56" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="W56" t="s">
         <v>34</v>
@@ -5412,7 +5409,7 @@
         <v>147</v>
       </c>
       <c r="Z56" s="2" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
@@ -5423,22 +5420,22 @@
         <v>26</v>
       </c>
       <c r="C57" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D57" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E57" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="F57" t="s">
         <v>52</v>
       </c>
       <c r="J57" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L57" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M57" t="s">
         <v>41</v>
@@ -5464,31 +5461,31 @@
         <v>26</v>
       </c>
       <c r="C58" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="D58" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="E58" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F58" t="s">
         <v>52</v>
       </c>
       <c r="J58" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L58" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M58" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="N58" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="V58" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="W58" t="s">
         <v>34</v>
@@ -5500,7 +5497,7 @@
         <v>147</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
@@ -5511,13 +5508,13 @@
         <v>26</v>
       </c>
       <c r="C59" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D59" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="E59" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="F59" t="s">
         <v>112</v>
@@ -5526,7 +5523,7 @@
         <v>113</v>
       </c>
       <c r="J59" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s">
         <v>41</v>
@@ -5552,19 +5549,19 @@
         <v>26</v>
       </c>
       <c r="C60" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D60" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E60" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F60" t="s">
         <v>52</v>
       </c>
       <c r="L60" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M60" t="s">
         <v>41</v>
@@ -5590,34 +5587,34 @@
         <v>26</v>
       </c>
       <c r="C61" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D61" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E61" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="F61" t="s">
         <v>52</v>
       </c>
       <c r="K61" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L61" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M61" t="s">
         <v>41</v>
       </c>
       <c r="V61" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="W61" t="s">
         <v>88</v>
       </c>
       <c r="X61" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y61" t="s">
         <v>88</v>
@@ -5634,22 +5631,22 @@
         <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D62" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E62" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F62" t="s">
         <v>52</v>
       </c>
       <c r="K62" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L62" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="M62" t="s">
         <v>41</v>
@@ -5675,31 +5672,31 @@
         <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D63" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E63" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F63" t="s">
         <v>52</v>
       </c>
       <c r="J63" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="K63" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L63" t="s">
         <v>93</v>
       </c>
       <c r="M63" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="N63" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="T63" t="s">
         <v>146</v>
@@ -5714,7 +5711,7 @@
         <v>147</v>
       </c>
       <c r="Z63" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -5725,19 +5722,19 @@
         <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D64" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="E64" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="F64" t="s">
         <v>52</v>
       </c>
       <c r="J64" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L64" t="s">
         <v>93</v>
@@ -5766,37 +5763,37 @@
         <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D65" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E65" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F65" t="s">
         <v>52</v>
       </c>
       <c r="J65" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="K65" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L65" t="s">
         <v>93</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="V65" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="W65" t="s">
         <v>34</v>
@@ -5808,7 +5805,7 @@
         <v>147</v>
       </c>
       <c r="Z65" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
@@ -5819,19 +5816,19 @@
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D66" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E66" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F66" t="s">
         <v>112</v>
       </c>
       <c r="J66" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="M66" t="s">
         <v>41</v>
@@ -5857,19 +5854,19 @@
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D67" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E67" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F67" t="s">
         <v>52</v>
       </c>
       <c r="G67" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="M67" t="s">
         <v>41</v>
@@ -5895,31 +5892,31 @@
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D68" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E68" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F68" t="s">
         <v>52</v>
       </c>
       <c r="K68" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="L68" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="M68" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="N68" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="T68" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="W68" t="s">
         <v>34</v>
@@ -5931,7 +5928,7 @@
         <v>72</v>
       </c>
       <c r="Z68" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -5942,37 +5939,37 @@
         <v>26</v>
       </c>
       <c r="C69" t="s">
+        <v>419</v>
+      </c>
+      <c r="D69" t="s">
+        <v>420</v>
+      </c>
+      <c r="E69" t="s">
+        <v>421</v>
+      </c>
+      <c r="F69" t="s">
+        <v>52</v>
+      </c>
+      <c r="J69" t="s">
+        <v>422</v>
+      </c>
+      <c r="K69" t="s">
+        <v>423</v>
+      </c>
+      <c r="L69" t="s">
+        <v>424</v>
+      </c>
+      <c r="M69" t="s">
+        <v>425</v>
+      </c>
+      <c r="N69" t="s">
+        <v>426</v>
+      </c>
+      <c r="T69" t="s">
+        <v>427</v>
+      </c>
+      <c r="V69" t="s">
         <v>428</v>
-      </c>
-      <c r="D69" t="s">
-        <v>429</v>
-      </c>
-      <c r="E69" t="s">
-        <v>430</v>
-      </c>
-      <c r="F69" t="s">
-        <v>52</v>
-      </c>
-      <c r="J69" t="s">
-        <v>431</v>
-      </c>
-      <c r="K69" t="s">
-        <v>432</v>
-      </c>
-      <c r="L69" t="s">
-        <v>433</v>
-      </c>
-      <c r="M69" t="s">
-        <v>434</v>
-      </c>
-      <c r="N69" t="s">
-        <v>435</v>
-      </c>
-      <c r="T69" t="s">
-        <v>436</v>
-      </c>
-      <c r="V69" t="s">
-        <v>437</v>
       </c>
       <c r="W69" t="s">
         <v>34</v>
@@ -5984,7 +5981,7 @@
         <v>147</v>
       </c>
       <c r="Z69" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
@@ -5995,37 +5992,37 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D70" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E70" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F70" t="s">
         <v>52</v>
       </c>
       <c r="I70" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="J70" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L70" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M70" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="N70" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="T70" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V70" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="W70" t="s">
         <v>34</v>
@@ -6037,7 +6034,7 @@
         <v>72</v>
       </c>
       <c r="Z70" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
@@ -6048,37 +6045,37 @@
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D71" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E71" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F71" t="s">
         <v>52</v>
       </c>
       <c r="I71" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J71" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L71" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M71" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="N71" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="T71" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V71" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="W71" t="s">
         <v>34</v>
@@ -6090,7 +6087,7 @@
         <v>72</v>
       </c>
       <c r="Z71" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
@@ -6101,25 +6098,25 @@
         <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D72" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E72" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F72" t="s">
         <v>52</v>
       </c>
       <c r="I72" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J72" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L72" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M72" t="s">
         <v>41</v>
@@ -6145,37 +6142,37 @@
         <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D73" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E73" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="F73" t="s">
         <v>52</v>
       </c>
       <c r="I73" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="J73" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L73" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M73" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="N73" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="T73" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V73" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W73" t="s">
         <v>34</v>
@@ -6187,7 +6184,7 @@
         <v>72</v>
       </c>
       <c r="Z73" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
@@ -6198,37 +6195,37 @@
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D74" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E74" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F74" t="s">
         <v>52</v>
       </c>
       <c r="I74" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="J74" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L74" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M74" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="N74" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="T74" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V74" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W74" t="s">
         <v>34</v>
@@ -6240,7 +6237,7 @@
         <v>72</v>
       </c>
       <c r="Z74" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
@@ -6251,37 +6248,37 @@
         <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D75" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E75" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F75" t="s">
         <v>52</v>
       </c>
       <c r="I75" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="J75" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L75" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M75" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="N75" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="T75" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V75" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W75" t="s">
         <v>34</v>
@@ -6293,7 +6290,7 @@
         <v>72</v>
       </c>
       <c r="Z75" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
@@ -6304,37 +6301,37 @@
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D76" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E76" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F76" t="s">
         <v>52</v>
       </c>
       <c r="I76" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="J76" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="K76" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="L76" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M76" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="T76" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W76" t="s">
         <v>34</v>
@@ -6346,7 +6343,7 @@
         <v>72</v>
       </c>
       <c r="Z76" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
@@ -6357,37 +6354,37 @@
         <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="D77" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E77" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F77" t="s">
         <v>52</v>
       </c>
       <c r="I77" t="s">
+        <v>470</v>
+      </c>
+      <c r="J77" t="s">
         <v>479</v>
       </c>
-      <c r="J77" t="s">
-        <v>488</v>
-      </c>
       <c r="L77" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M77" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="N77" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="T77" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V77" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="W77" t="s">
         <v>34</v>
@@ -6399,10 +6396,10 @@
         <v>72</v>
       </c>
       <c r="Z77" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="AA77" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="78" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -6413,34 +6410,34 @@
         <v>26</v>
       </c>
       <c r="C78" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D78" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E78" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F78" t="s">
         <v>52</v>
       </c>
       <c r="J78" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="L78" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M78" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="N78" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="T78" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="V78" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="W78" t="s">
         <v>34</v>
@@ -6452,7 +6449,7 @@
         <v>147</v>
       </c>
       <c r="Z78" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
@@ -6463,37 +6460,37 @@
         <v>26</v>
       </c>
       <c r="C79" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="D79" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="E79" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F79" t="s">
         <v>52</v>
       </c>
       <c r="I79" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="J79" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="K79" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="L79" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M79" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="N79" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="T79" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W79" t="s">
         <v>34</v>
@@ -6505,7 +6502,7 @@
         <v>72</v>
       </c>
       <c r="Z79" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.25">
@@ -6516,22 +6513,22 @@
         <v>26</v>
       </c>
       <c r="C80" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D80" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="E80" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="F80" t="s">
         <v>52</v>
       </c>
       <c r="K80" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="L80" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="M80" t="s">
         <v>41</v>
@@ -6557,34 +6554,34 @@
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="D81" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E81" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="F81" t="s">
         <v>52</v>
       </c>
       <c r="J81" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="K81" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="L81" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M81" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="N81" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T81" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W81" t="s">
         <v>34</v>
@@ -6596,7 +6593,7 @@
         <v>72</v>
       </c>
       <c r="Z81" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="82" spans="1:26" x14ac:dyDescent="0.25">
@@ -6607,22 +6604,22 @@
         <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D82" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E82" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="F82" t="s">
         <v>52</v>
       </c>
       <c r="J82" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L82" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M82" t="s">
         <v>41</v>
@@ -6648,22 +6645,22 @@
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D83" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E83" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="F83" t="s">
         <v>52</v>
       </c>
       <c r="J83" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L83" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M83" t="s">
         <v>41</v>
@@ -6689,22 +6686,22 @@
         <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D84" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E84" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="F84" t="s">
         <v>52</v>
       </c>
       <c r="J84" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L84" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M84" t="s">
         <v>41</v>
@@ -6730,22 +6727,22 @@
         <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="D85" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E85" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="F85" t="s">
         <v>52</v>
       </c>
       <c r="J85" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L85" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M85" t="s">
         <v>41</v>
@@ -6771,22 +6768,22 @@
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D86" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E86" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="F86" t="s">
         <v>52</v>
       </c>
       <c r="J86" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L86" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M86" t="s">
         <v>41</v>
@@ -6812,22 +6809,22 @@
         <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D87" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E87" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="F87" t="s">
         <v>52</v>
       </c>
       <c r="J87" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L87" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M87" t="s">
         <v>41</v>
@@ -6853,22 +6850,22 @@
         <v>26</v>
       </c>
       <c r="C88" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D88" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E88" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="F88" t="s">
         <v>52</v>
       </c>
       <c r="J88" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L88" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M88" t="s">
         <v>41</v>
@@ -6894,22 +6891,22 @@
         <v>26</v>
       </c>
       <c r="C89" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D89" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E89" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F89" t="s">
         <v>52</v>
       </c>
       <c r="J89" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L89" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M89" t="s">
         <v>41</v>
@@ -6935,22 +6932,22 @@
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D90" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E90" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="F90" t="s">
         <v>52</v>
       </c>
       <c r="J90" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L90" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M90" t="s">
         <v>41</v>
@@ -6976,22 +6973,22 @@
         <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D91" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E91" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="F91" t="s">
         <v>52</v>
       </c>
       <c r="J91" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L91" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M91" t="s">
         <v>41</v>
@@ -7017,22 +7014,22 @@
         <v>26</v>
       </c>
       <c r="C92" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D92" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E92" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="F92" t="s">
         <v>52</v>
       </c>
       <c r="J92" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L92" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M92" t="s">
         <v>41</v>
@@ -7058,22 +7055,22 @@
         <v>26</v>
       </c>
       <c r="C93" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D93" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E93" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="F93" t="s">
         <v>52</v>
       </c>
       <c r="J93" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L93" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M93" t="s">
         <v>41</v>
@@ -7099,22 +7096,22 @@
         <v>26</v>
       </c>
       <c r="C94" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D94" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E94" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="F94" t="s">
         <v>52</v>
       </c>
       <c r="J94" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L94" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M94" t="s">
         <v>41</v>
@@ -7140,22 +7137,22 @@
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D95" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E95" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="F95" t="s">
         <v>52</v>
       </c>
       <c r="J95" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L95" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M95" t="s">
         <v>41</v>
@@ -7181,22 +7178,22 @@
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D96" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="E96" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="F96" t="s">
         <v>52</v>
       </c>
       <c r="J96" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L96" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M96" t="s">
         <v>41</v>
@@ -7222,22 +7219,22 @@
         <v>26</v>
       </c>
       <c r="C97" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D97" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E97" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="F97" t="s">
         <v>52</v>
       </c>
       <c r="J97" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L97" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M97" t="s">
         <v>41</v>
@@ -7263,22 +7260,22 @@
         <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D98" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="E98" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="F98" t="s">
         <v>52</v>
       </c>
       <c r="J98" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L98" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M98" t="s">
         <v>41</v>
@@ -7304,22 +7301,22 @@
         <v>26</v>
       </c>
       <c r="C99" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D99" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="E99" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="F99" t="s">
         <v>52</v>
       </c>
       <c r="J99" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L99" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M99" t="s">
         <v>41</v>
@@ -7345,22 +7342,22 @@
         <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D100" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="E100" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="F100" t="s">
         <v>52</v>
       </c>
       <c r="J100" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L100" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M100" t="s">
         <v>41</v>
@@ -7386,22 +7383,22 @@
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D101" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="E101" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="F101" t="s">
         <v>52</v>
       </c>
       <c r="J101" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="L101" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M101" t="s">
         <v>41</v>
@@ -7427,34 +7424,34 @@
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D102" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E102" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="F102" t="s">
         <v>52</v>
       </c>
       <c r="J102" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="L102" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M102" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="N102" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="T102" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V102" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="W102" t="s">
         <v>34</v>
@@ -7466,7 +7463,7 @@
         <v>72</v>
       </c>
       <c r="Z102" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="103" spans="1:26" x14ac:dyDescent="0.25">
@@ -7477,31 +7474,31 @@
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D103" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E103" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="F103" t="s">
         <v>52</v>
       </c>
       <c r="J103" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="L103" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M103" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="N103" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="T103" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W103" t="s">
         <v>34</v>
@@ -7513,7 +7510,7 @@
         <v>72</v>
       </c>
       <c r="Z103" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:26" x14ac:dyDescent="0.25">
@@ -7524,22 +7521,22 @@
         <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D104" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E104" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F104" t="s">
         <v>52</v>
       </c>
       <c r="J104" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="L104" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M104" t="s">
         <v>41</v>
@@ -7565,25 +7562,25 @@
         <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D105" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E105" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="F105" t="s">
         <v>52</v>
       </c>
       <c r="J105" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L105" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M105" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="W105" t="s">
         <v>34</v>
@@ -7595,7 +7592,7 @@
         <v>72</v>
       </c>
       <c r="Z105" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="106" spans="1:26" x14ac:dyDescent="0.25">
@@ -7606,22 +7603,22 @@
         <v>26</v>
       </c>
       <c r="C106" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D106" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="E106" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="F106" t="s">
         <v>52</v>
       </c>
       <c r="J106" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L106" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M106" t="s">
         <v>41</v>
@@ -7647,19 +7644,19 @@
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D107" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E107" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="F107" t="s">
         <v>52</v>
       </c>
       <c r="J107" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="M107" t="s">
         <v>41</v>
@@ -7685,19 +7682,19 @@
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D108" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E108" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="F108" t="s">
         <v>52</v>
       </c>
       <c r="J108" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M108" t="s">
         <v>41</v>
@@ -7723,19 +7720,19 @@
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D109" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="E109" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="F109" t="s">
         <v>52</v>
       </c>
       <c r="J109" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="M109" t="s">
         <v>41</v>
@@ -7761,19 +7758,19 @@
         <v>26</v>
       </c>
       <c r="C110" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="D110" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E110" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="F110" t="s">
         <v>52</v>
       </c>
       <c r="J110" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="M110" t="s">
         <v>41</v>
@@ -7799,19 +7796,19 @@
         <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D111" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E111" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F111" t="s">
         <v>52</v>
       </c>
       <c r="J111" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="M111" t="s">
         <v>41</v>
@@ -7837,19 +7834,19 @@
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D112" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E112" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F112" t="s">
         <v>52</v>
       </c>
       <c r="J112" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M112" t="s">
         <v>41</v>
@@ -7875,19 +7872,19 @@
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D113" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E113" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="F113" t="s">
         <v>52</v>
       </c>
       <c r="J113" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M113" t="s">
         <v>41</v>
@@ -7910,7 +7907,7 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C114" t="s">
         <v>27</v>
@@ -7952,7 +7949,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -7991,7 +7988,7 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C116" t="s">
         <v>44</v>
@@ -8030,7 +8027,7 @@
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C117" t="s">
         <v>49</v>
@@ -8061,7 +8058,7 @@
         <v>42</v>
       </c>
       <c r="Z117" s="7" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
@@ -8069,7 +8066,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C118" t="s">
         <v>55</v>
@@ -8093,7 +8090,7 @@
         <v>61</v>
       </c>
       <c r="M118" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="N118" t="s">
         <v>63</v>
@@ -8117,7 +8114,7 @@
         <v>6</v>
       </c>
       <c r="B119" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C119" t="s">
         <v>65</v>
@@ -8135,7 +8132,7 @@
         <v>68</v>
       </c>
       <c r="M119" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="N119" t="s">
         <v>70</v>
@@ -8161,7 +8158,7 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C120" t="s">
         <v>74</v>
@@ -8185,7 +8182,7 @@
         <v>79</v>
       </c>
       <c r="M120" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="N120" t="s">
         <v>81</v>
@@ -8209,7 +8206,7 @@
         <v>8</v>
       </c>
       <c r="B121" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C121" t="s">
         <v>82</v>
@@ -8254,7 +8251,7 @@
         <v>9</v>
       </c>
       <c r="B122" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C122" t="s">
         <v>90</v>
@@ -8299,7 +8296,7 @@
         <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C123" t="s">
         <v>94</v>
@@ -8320,7 +8317,7 @@
         <v>98</v>
       </c>
       <c r="M123" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="N123" t="s">
         <v>100</v>
@@ -8349,7 +8346,7 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C124" t="s">
         <v>104</v>
@@ -8394,7 +8391,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C125" t="s">
         <v>110</v>
@@ -8433,7 +8430,7 @@
         <v>13</v>
       </c>
       <c r="B126" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C126" t="s">
         <v>114</v>
@@ -8448,7 +8445,7 @@
         <v>30</v>
       </c>
       <c r="M126" t="s">
-        <v>628</v>
+        <v>41</v>
       </c>
       <c r="T126" s="2"/>
       <c r="W126" t="s">
@@ -8469,7 +8466,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C127" t="s">
         <v>117</v>
@@ -8490,7 +8487,7 @@
         <v>121</v>
       </c>
       <c r="M127" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="N127" t="s">
         <v>100</v>
@@ -8516,7 +8513,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C128" t="s">
         <v>123</v>
@@ -8534,7 +8531,7 @@
         <v>126</v>
       </c>
       <c r="M128" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="N128" t="s">
         <v>128</v>
@@ -8563,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="B129" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C129" t="s">
         <v>132</v>
@@ -8608,7 +8605,7 @@
         <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C130" t="s">
         <v>138</v>
@@ -8632,10 +8629,10 @@
         <v>143</v>
       </c>
       <c r="M130" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="T130" s="2"/>
       <c r="W130" t="s">
@@ -8648,7 +8645,7 @@
         <v>147</v>
       </c>
       <c r="Z130" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="131" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -8656,7 +8653,7 @@
         <v>18</v>
       </c>
       <c r="B131" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C131" t="s">
         <v>149</v>
@@ -8674,7 +8671,7 @@
         <v>151</v>
       </c>
       <c r="M131" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="N131" t="s">
         <v>145</v>
@@ -8690,7 +8687,7 @@
         <v>147</v>
       </c>
       <c r="Z131" s="2" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
     </row>
     <row r="132" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -8698,7 +8695,7 @@
         <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C132" t="s">
         <v>153</v>
@@ -8722,7 +8719,7 @@
         <v>143</v>
       </c>
       <c r="M132" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="N132" t="s">
         <v>158</v>
@@ -8738,7 +8735,7 @@
         <v>147</v>
       </c>
       <c r="Z132" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
     <row r="133" spans="1:27" ht="60" x14ac:dyDescent="0.25">
@@ -8746,7 +8743,7 @@
         <v>20</v>
       </c>
       <c r="B133" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C133" t="s">
         <v>160</v>
@@ -8764,7 +8761,7 @@
         <v>151</v>
       </c>
       <c r="M133" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="N133" t="s">
         <v>158</v>
@@ -8780,7 +8777,7 @@
         <v>147</v>
       </c>
       <c r="Z133" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
     </row>
     <row r="134" spans="1:27" x14ac:dyDescent="0.25">
@@ -8788,7 +8785,7 @@
         <v>21</v>
       </c>
       <c r="B134" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C134" t="s">
         <v>163</v>
@@ -8812,10 +8809,10 @@
         <v>143</v>
       </c>
       <c r="M134" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="N134" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="T134" s="2"/>
       <c r="W134" t="s">
@@ -8828,7 +8825,7 @@
         <v>169</v>
       </c>
       <c r="Z134" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
     </row>
     <row r="135" spans="1:27" x14ac:dyDescent="0.25">
@@ -8836,7 +8833,7 @@
         <v>22</v>
       </c>
       <c r="B135" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C135" t="s">
         <v>171</v>
@@ -8860,7 +8857,7 @@
         <v>143</v>
       </c>
       <c r="M135" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="N135" t="s">
         <v>175</v>
@@ -8876,7 +8873,7 @@
         <v>169</v>
       </c>
       <c r="Z135" s="2" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
     </row>
     <row r="136" spans="1:27" x14ac:dyDescent="0.25">
@@ -8884,7 +8881,7 @@
         <v>23</v>
       </c>
       <c r="B136" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C136" t="s">
         <v>177</v>
@@ -8902,7 +8899,7 @@
         <v>151</v>
       </c>
       <c r="M136" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="N136" t="s">
         <v>175</v>
@@ -8918,7 +8915,7 @@
         <v>169</v>
       </c>
       <c r="Z136" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
     </row>
     <row r="137" spans="1:27" x14ac:dyDescent="0.25">
@@ -8926,7 +8923,7 @@
         <v>24</v>
       </c>
       <c r="B137" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C137" t="s">
         <v>180</v>
@@ -8944,7 +8941,7 @@
         <v>183</v>
       </c>
       <c r="M137" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="N137" t="s">
         <v>185</v>
@@ -8960,7 +8957,7 @@
         <v>169</v>
       </c>
       <c r="Z137" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.25">
@@ -8968,7 +8965,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C138" t="s">
         <v>187</v>
@@ -8983,7 +8980,7 @@
         <v>30</v>
       </c>
       <c r="M138" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="N138" t="s">
         <v>185</v>
@@ -8999,7 +8996,7 @@
         <v>169</v>
       </c>
       <c r="Z138" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
     </row>
     <row r="139" spans="1:27" x14ac:dyDescent="0.25">
@@ -9007,7 +9004,7 @@
         <v>26</v>
       </c>
       <c r="B139" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C139" t="s">
         <v>191</v>
@@ -9031,7 +9028,7 @@
         <v>196</v>
       </c>
       <c r="M139" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="N139" t="s">
         <v>198</v>
@@ -9050,7 +9047,7 @@
         <v>169</v>
       </c>
       <c r="Z139" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.25">
@@ -9058,7 +9055,7 @@
         <v>27</v>
       </c>
       <c r="B140" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C140" t="s">
         <v>201</v>
@@ -9082,7 +9079,7 @@
         <v>196</v>
       </c>
       <c r="M140" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="N140" t="s">
         <v>205</v>
@@ -9101,7 +9098,7 @@
         <v>169</v>
       </c>
       <c r="Z140" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.25">
@@ -9109,7 +9106,7 @@
         <v>28</v>
       </c>
       <c r="B141" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C141" t="s">
         <v>207</v>
@@ -9133,7 +9130,7 @@
         <v>211</v>
       </c>
       <c r="M141" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="N141" t="s">
         <v>213</v>
@@ -9149,7 +9146,7 @@
         <v>169</v>
       </c>
       <c r="Z141" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.25">
@@ -9157,7 +9154,7 @@
         <v>29</v>
       </c>
       <c r="B142" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C142" t="s">
         <v>215</v>
@@ -9202,7 +9199,7 @@
         <v>30</v>
       </c>
       <c r="B143" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C143" t="s">
         <v>220</v>
@@ -9220,16 +9217,16 @@
         <v>223</v>
       </c>
       <c r="M143" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="N143" t="s">
         <v>225</v>
       </c>
       <c r="T143" s="2" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="V143" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="W143" t="s">
         <v>34</v>
@@ -9241,10 +9238,10 @@
         <v>72</v>
       </c>
       <c r="Z143" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="AA143" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.25">
@@ -9252,7 +9249,7 @@
         <v>31</v>
       </c>
       <c r="B144" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C144" t="s">
         <v>229</v>
@@ -9270,7 +9267,7 @@
         <v>231</v>
       </c>
       <c r="M144" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="N144" t="s">
         <v>233</v>
@@ -9286,7 +9283,7 @@
         <v>169</v>
       </c>
       <c r="Z144" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.25">
@@ -9294,7 +9291,7 @@
         <v>32</v>
       </c>
       <c r="B145" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C145" t="s">
         <v>235</v>
@@ -9312,7 +9309,7 @@
         <v>237</v>
       </c>
       <c r="M145" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="N145" t="s">
         <v>239</v>
@@ -9328,7 +9325,7 @@
         <v>169</v>
       </c>
       <c r="Z145" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.25">
@@ -9336,28 +9333,28 @@
         <v>33</v>
       </c>
       <c r="B146" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C146" t="s">
+        <v>240</v>
+      </c>
+      <c r="D146" t="s">
         <v>241</v>
       </c>
-      <c r="D146" t="s">
-        <v>242</v>
-      </c>
       <c r="E146" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F146" t="s">
         <v>112</v>
       </c>
       <c r="G146" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M146" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="N146" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T146" s="2"/>
       <c r="W146" t="s">
@@ -9370,7 +9367,7 @@
         <v>169</v>
       </c>
       <c r="Z146" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
     </row>
     <row r="147" spans="1:27" x14ac:dyDescent="0.25">
@@ -9378,28 +9375,28 @@
         <v>34</v>
       </c>
       <c r="B147" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C147" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D147" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E147" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F147" t="s">
         <v>112</v>
       </c>
       <c r="G147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M147" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="N147" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="T147" s="2"/>
       <c r="W147" t="s">
@@ -9412,7 +9409,7 @@
         <v>169</v>
       </c>
       <c r="Z147" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
     </row>
     <row r="148" spans="1:27" x14ac:dyDescent="0.25">
@@ -9420,28 +9417,28 @@
         <v>35</v>
       </c>
       <c r="B148" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C148" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D148" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E148" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F148" t="s">
         <v>112</v>
       </c>
       <c r="G148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M148" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="N148" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="T148" s="2"/>
       <c r="W148" t="s">
@@ -9454,7 +9451,7 @@
         <v>169</v>
       </c>
       <c r="Z148" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
     </row>
     <row r="149" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -9462,34 +9459,34 @@
         <v>36</v>
       </c>
       <c r="B149" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C149" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D149" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E149" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F149" t="s">
         <v>112</v>
       </c>
       <c r="G149" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J149" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="N149" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="T149" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="W149" t="s">
         <v>34</v>
@@ -9501,7 +9498,7 @@
         <v>147</v>
       </c>
       <c r="Z149" s="2" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
     </row>
     <row r="150" spans="1:27" x14ac:dyDescent="0.25">
@@ -9509,28 +9506,28 @@
         <v>37</v>
       </c>
       <c r="B150" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D150" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E150" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F150" t="s">
         <v>112</v>
       </c>
       <c r="G150" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M150" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="N150" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="T150" s="2"/>
       <c r="W150" t="s">
@@ -9543,7 +9540,7 @@
         <v>169</v>
       </c>
       <c r="Z150" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
     </row>
     <row r="151" spans="1:27" x14ac:dyDescent="0.25">
@@ -9551,28 +9548,28 @@
         <v>38</v>
       </c>
       <c r="B151" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F151" t="s">
         <v>112</v>
       </c>
       <c r="G151" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="M151" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="N151" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="T151" s="2"/>
       <c r="W151" t="s">
@@ -9585,7 +9582,7 @@
         <v>169</v>
       </c>
       <c r="Z151" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
     </row>
     <row r="152" spans="1:27" x14ac:dyDescent="0.25">
@@ -9593,28 +9590,28 @@
         <v>39</v>
       </c>
       <c r="B152" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C152" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E152" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F152" t="s">
         <v>112</v>
       </c>
       <c r="G152" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J152" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="K152" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M152" t="s">
         <v>41</v>
@@ -9638,25 +9635,25 @@
         <v>40</v>
       </c>
       <c r="B153" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C153" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="D153" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E153" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="F153" t="s">
         <v>52</v>
       </c>
       <c r="K153" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L153" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M153" t="s">
         <v>41</v>
@@ -9680,28 +9677,28 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C154" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D154" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E154" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F154" t="s">
         <v>112</v>
       </c>
       <c r="G154" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="J154" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="K154" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M154" t="s">
         <v>41</v>
@@ -9725,28 +9722,28 @@
         <v>42</v>
       </c>
       <c r="B155" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C155" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D155" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E155" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F155" t="s">
         <v>52</v>
       </c>
       <c r="J155" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="K155" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="L155" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M155" t="s">
         <v>41</v>
@@ -9770,22 +9767,22 @@
         <v>43</v>
       </c>
       <c r="B156" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C156" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D156" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E156" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F156" t="s">
         <v>112</v>
       </c>
       <c r="G156" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M156" t="s">
         <v>41</v>
@@ -9809,35 +9806,35 @@
         <v>44</v>
       </c>
       <c r="B157" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C157" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D157" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E157" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="F157" t="s">
         <v>112</v>
       </c>
       <c r="G157" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="J157" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="K157" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M157" t="s">
         <v>41</v>
       </c>
       <c r="T157" s="2"/>
       <c r="W157" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="X157" t="s">
         <v>89</v>
@@ -9849,7 +9846,7 @@
         <v>88</v>
       </c>
       <c r="AA157" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="158" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
@@ -9857,31 +9854,31 @@
         <v>45</v>
       </c>
       <c r="B158" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C158" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D158" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E158" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F158" t="s">
         <v>52</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="M158" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="N158" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="T158" s="2" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="W158" t="s">
         <v>34</v>
@@ -9893,7 +9890,7 @@
         <v>72</v>
       </c>
       <c r="Z158" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="159" spans="1:27" ht="390" x14ac:dyDescent="0.25">
@@ -9901,40 +9898,40 @@
         <v>46</v>
       </c>
       <c r="B159" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C159" t="s">
+        <v>301</v>
+      </c>
+      <c r="D159" t="s">
+        <v>302</v>
+      </c>
+      <c r="E159" t="s">
+        <v>302</v>
+      </c>
+      <c r="F159" t="s">
+        <v>52</v>
+      </c>
+      <c r="J159" t="s">
+        <v>303</v>
+      </c>
+      <c r="K159" t="s">
+        <v>304</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="M159" t="s">
+        <v>669</v>
+      </c>
+      <c r="N159" t="s">
+        <v>307</v>
+      </c>
+      <c r="T159" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D159" t="s">
-        <v>309</v>
-      </c>
-      <c r="E159" t="s">
-        <v>309</v>
-      </c>
-      <c r="F159" t="s">
-        <v>52</v>
-      </c>
-      <c r="J159" t="s">
-        <v>310</v>
-      </c>
-      <c r="K159" t="s">
-        <v>311</v>
-      </c>
-      <c r="L159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M159" t="s">
-        <v>679</v>
-      </c>
-      <c r="N159" t="s">
-        <v>314</v>
-      </c>
-      <c r="T159" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="V159" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="W159" t="s">
         <v>34</v>
@@ -9946,7 +9943,7 @@
         <v>72</v>
       </c>
       <c r="Z159" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:27" ht="390" x14ac:dyDescent="0.25">
@@ -9954,34 +9951,34 @@
         <v>47</v>
       </c>
       <c r="B160" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C160" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D160" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E160" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F160" t="s">
         <v>52</v>
       </c>
       <c r="K160" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="L160" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="M160" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="N160" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="T160" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="W160" t="s">
         <v>34</v>
@@ -9993,7 +9990,7 @@
         <v>72</v>
       </c>
       <c r="Z160" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="161" spans="1:26" x14ac:dyDescent="0.25">
@@ -10001,34 +9998,34 @@
         <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C161" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D161" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="E161" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F161" t="s">
         <v>112</v>
       </c>
       <c r="G161" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J161" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="K161" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="M161" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="N161" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="T161" s="2"/>
       <c r="W161" t="s">
@@ -10041,7 +10038,7 @@
         <v>169</v>
       </c>
       <c r="Z161" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="162" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -10049,16 +10046,16 @@
         <v>49</v>
       </c>
       <c r="B162" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C162" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D162" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E162" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="F162" t="s">
         <v>112</v>
@@ -10067,10 +10064,10 @@
         <v>113</v>
       </c>
       <c r="M162" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="N162" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="T162" s="2" t="s">
         <v>146</v>
@@ -10085,7 +10082,7 @@
         <v>169</v>
       </c>
       <c r="Z162" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
     </row>
     <row r="163" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -10093,31 +10090,31 @@
         <v>50</v>
       </c>
       <c r="B163" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C163" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D163" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="E163" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F163" t="s">
         <v>52</v>
       </c>
       <c r="J163" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="L163" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="M163" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="N163" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="T163" s="2" t="s">
         <v>146</v>
@@ -10132,7 +10129,7 @@
         <v>147</v>
       </c>
       <c r="Z163" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
     </row>
     <row r="164" spans="1:26" ht="180" x14ac:dyDescent="0.25">
@@ -10140,34 +10137,34 @@
         <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C164" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D164" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E164" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="F164" t="s">
         <v>52</v>
       </c>
       <c r="K164" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="L164" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="M164" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="N164" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="T164" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="W164" t="s">
         <v>34</v>
@@ -10179,7 +10176,7 @@
         <v>72</v>
       </c>
       <c r="Z164" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="165" spans="1:26" ht="165" x14ac:dyDescent="0.25">
@@ -10187,31 +10184,31 @@
         <v>52</v>
       </c>
       <c r="B165" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C165" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="D165" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E165" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F165" t="s">
         <v>52</v>
       </c>
       <c r="J165" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M165" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="N165" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="T165" s="2"/>
       <c r="W165" t="s">
@@ -10224,7 +10221,7 @@
         <v>147</v>
       </c>
       <c r="Z165" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="166" spans="1:26" ht="165" x14ac:dyDescent="0.25">
@@ -10232,22 +10229,22 @@
         <v>53</v>
       </c>
       <c r="B166" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C166" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D166" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E166" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F166" t="s">
         <v>52</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M166" t="s">
         <v>41</v>
@@ -10271,22 +10268,22 @@
         <v>54</v>
       </c>
       <c r="B167" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C167" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D167" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E167" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F167" t="s">
         <v>52</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M167" t="s">
         <v>41</v>
@@ -10310,28 +10307,28 @@
         <v>55</v>
       </c>
       <c r="B168" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C168" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D168" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E168" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F168" t="s">
         <v>52</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="M168" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="N168" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="T168" s="2"/>
       <c r="W168" t="s">
@@ -10344,7 +10341,7 @@
         <v>147</v>
       </c>
       <c r="Z168" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
     </row>
     <row r="169" spans="1:26" ht="165" x14ac:dyDescent="0.25">
@@ -10352,25 +10349,25 @@
         <v>56</v>
       </c>
       <c r="B169" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C169" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D169" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E169" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="F169" t="s">
         <v>52</v>
       </c>
       <c r="J169" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M169" t="s">
         <v>41</v>
@@ -10394,31 +10391,31 @@
         <v>57</v>
       </c>
       <c r="B170" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C170" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="D170" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="E170" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F170" t="s">
         <v>52</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="M170" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="N170" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="T170" s="2"/>
       <c r="W170" t="s">
@@ -10431,7 +10428,7 @@
         <v>147</v>
       </c>
       <c r="Z170" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
     </row>
     <row r="171" spans="1:26" x14ac:dyDescent="0.25">
@@ -10439,16 +10436,16 @@
         <v>58</v>
       </c>
       <c r="B171" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C171" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="D171" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="E171" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="F171" t="s">
         <v>112</v>
@@ -10457,7 +10454,7 @@
         <v>113</v>
       </c>
       <c r="J171" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" t="s">
@@ -10482,22 +10479,22 @@
         <v>59</v>
       </c>
       <c r="B172" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C172" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D172" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E172" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F172" t="s">
         <v>52</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M172" t="s">
         <v>41</v>
@@ -10521,38 +10518,38 @@
         <v>60</v>
       </c>
       <c r="B173" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C173" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D173" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E173" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="F173" t="s">
         <v>52</v>
       </c>
       <c r="K173" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="M173" t="s">
         <v>41</v>
       </c>
       <c r="T173" s="2"/>
       <c r="V173" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="W173" t="s">
         <v>88</v>
       </c>
       <c r="X173" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y173" t="s">
         <v>88</v>
@@ -10566,34 +10563,34 @@
         <v>61</v>
       </c>
       <c r="B174" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C174" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D174" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E174" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F174" t="s">
         <v>52</v>
       </c>
       <c r="K174" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="M174" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="N174" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="T174" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="W174" t="s">
         <v>34</v>
@@ -10605,7 +10602,7 @@
         <v>72</v>
       </c>
       <c r="Z174" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
     </row>
     <row r="175" spans="1:26" ht="30" x14ac:dyDescent="0.25">
@@ -10613,34 +10610,34 @@
         <v>62</v>
       </c>
       <c r="B175" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C175" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D175" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E175" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F175" t="s">
         <v>52</v>
       </c>
       <c r="J175" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="K175" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L175" t="s">
         <v>93</v>
       </c>
       <c r="M175" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="N175" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="T175" s="2" t="s">
         <v>146</v>
@@ -10655,7 +10652,7 @@
         <v>147</v>
       </c>
       <c r="Z175" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
     </row>
     <row r="176" spans="1:26" x14ac:dyDescent="0.25">
@@ -10663,22 +10660,22 @@
         <v>63</v>
       </c>
       <c r="B176" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C176" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D176" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="E176" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="F176" t="s">
         <v>52</v>
       </c>
       <c r="J176" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L176" t="s">
         <v>93</v>
@@ -10705,40 +10702,40 @@
         <v>64</v>
       </c>
       <c r="B177" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C177" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="D177" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="E177" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F177" t="s">
         <v>52</v>
       </c>
       <c r="J177" s="3" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="K177" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="L177" t="s">
         <v>93</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="T177" s="2" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="V177" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="W177" t="s">
         <v>34</v>
@@ -10750,7 +10747,7 @@
         <v>147</v>
       </c>
       <c r="Z177" s="2" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:27" x14ac:dyDescent="0.25">
@@ -10758,22 +10755,22 @@
         <v>65</v>
       </c>
       <c r="B178" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C178" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D178" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E178" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F178" t="s">
         <v>112</v>
       </c>
       <c r="J178" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="M178" t="s">
         <v>41</v>
@@ -10797,22 +10794,22 @@
         <v>66</v>
       </c>
       <c r="B179" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C179" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E179" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F179" t="s">
         <v>52</v>
       </c>
       <c r="G179" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="M179" t="s">
         <v>41</v>
@@ -10836,34 +10833,34 @@
         <v>67</v>
       </c>
       <c r="B180" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C180" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E180" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F180" t="s">
         <v>52</v>
       </c>
       <c r="K180" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="L180" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="M180" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="N180" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="T180" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="W180" t="s">
         <v>34</v>
@@ -10875,7 +10872,7 @@
         <v>72</v>
       </c>
       <c r="Z180" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="181" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
@@ -10883,40 +10880,40 @@
         <v>68</v>
       </c>
       <c r="B181" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C181" t="s">
+        <v>419</v>
+      </c>
+      <c r="D181" t="s">
+        <v>420</v>
+      </c>
+      <c r="E181" t="s">
+        <v>421</v>
+      </c>
+      <c r="F181" t="s">
+        <v>52</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="K181" t="s">
+        <v>423</v>
+      </c>
+      <c r="L181" t="s">
+        <v>424</v>
+      </c>
+      <c r="M181" t="s">
+        <v>694</v>
+      </c>
+      <c r="N181" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="T181" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="V181" t="s">
         <v>428</v>
-      </c>
-      <c r="D181" t="s">
-        <v>429</v>
-      </c>
-      <c r="E181" t="s">
-        <v>430</v>
-      </c>
-      <c r="F181" t="s">
-        <v>52</v>
-      </c>
-      <c r="J181" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K181" t="s">
-        <v>432</v>
-      </c>
-      <c r="L181" t="s">
-        <v>433</v>
-      </c>
-      <c r="M181" t="s">
-        <v>704</v>
-      </c>
-      <c r="N181" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="T181" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="V181" t="s">
-        <v>437</v>
       </c>
       <c r="W181" t="s">
         <v>34</v>
@@ -10928,7 +10925,7 @@
         <v>147</v>
       </c>
       <c r="Z181" s="2" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
     </row>
     <row r="182" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -10936,40 +10933,40 @@
         <v>69</v>
       </c>
       <c r="B182" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C182" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D182" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E182" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F182" t="s">
         <v>52</v>
       </c>
       <c r="I182" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="J182" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L182" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M182" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="N182" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="T182" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V182" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="W182" t="s">
         <v>34</v>
@@ -10981,7 +10978,7 @@
         <v>72</v>
       </c>
       <c r="Z182" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="183" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -10989,40 +10986,40 @@
         <v>70</v>
       </c>
       <c r="B183" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C183" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E183" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F183" t="s">
         <v>52</v>
       </c>
       <c r="I183" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J183" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L183" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M183" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="N183" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="T183" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V183" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="W183" t="s">
         <v>34</v>
@@ -11034,7 +11031,7 @@
         <v>72</v>
       </c>
       <c r="Z183" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="184" spans="1:27" x14ac:dyDescent="0.25">
@@ -11042,28 +11039,28 @@
         <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C184" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D184" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E184" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F184" t="s">
         <v>52</v>
       </c>
       <c r="I184" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J184" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L184" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M184" t="s">
         <v>41</v>
@@ -11087,40 +11084,40 @@
         <v>72</v>
       </c>
       <c r="B185" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C185" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D185" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="E185" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="F185" t="s">
         <v>52</v>
       </c>
       <c r="I185" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="J185" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L185" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M185" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="N185" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="T185" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V185" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W185" t="s">
         <v>34</v>
@@ -11132,7 +11129,7 @@
         <v>72</v>
       </c>
       <c r="Z185" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -11140,40 +11137,40 @@
         <v>73</v>
       </c>
       <c r="B186" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C186" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D186" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E186" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F186" t="s">
         <v>52</v>
       </c>
       <c r="I186" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="J186" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L186" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M186" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="N186" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="T186" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V186" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W186" t="s">
         <v>34</v>
@@ -11185,7 +11182,7 @@
         <v>72</v>
       </c>
       <c r="Z186" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -11193,40 +11190,40 @@
         <v>74</v>
       </c>
       <c r="B187" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C187" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D187" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E187" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F187" t="s">
         <v>52</v>
       </c>
       <c r="I187" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="J187" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L187" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M187" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="N187" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="T187" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V187" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="W187" t="s">
         <v>34</v>
@@ -11238,7 +11235,7 @@
         <v>72</v>
       </c>
       <c r="Z187" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -11246,40 +11243,40 @@
         <v>75</v>
       </c>
       <c r="B188" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C188" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D188" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E188" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F188" t="s">
         <v>52</v>
       </c>
       <c r="I188" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="J188" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="K188" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="L188" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M188" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="N188" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="T188" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W188" t="s">
         <v>34</v>
@@ -11291,7 +11288,7 @@
         <v>72</v>
       </c>
       <c r="Z188" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="1:27" ht="105" x14ac:dyDescent="0.25">
@@ -11299,40 +11296,40 @@
         <v>76</v>
       </c>
       <c r="B189" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C189" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="D189" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="E189" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F189" t="s">
         <v>52</v>
       </c>
       <c r="I189" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="J189" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="L189" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M189" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="N189" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="T189" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="V189" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="W189" t="s">
         <v>34</v>
@@ -11344,10 +11341,10 @@
         <v>72</v>
       </c>
       <c r="Z189" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="AA189" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
     </row>
     <row r="190" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
@@ -11355,40 +11352,40 @@
         <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C190" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D190" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E190" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F190" t="s">
         <v>52</v>
       </c>
       <c r="I190" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="J190" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="L190" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M190" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="T190" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="V190" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="W190" t="s">
         <v>34</v>
@@ -11400,7 +11397,7 @@
         <v>147</v>
       </c>
       <c r="Z190" s="2" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
     </row>
     <row r="191" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -11408,40 +11405,40 @@
         <v>78</v>
       </c>
       <c r="B191" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C191" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="D191" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="E191" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F191" t="s">
         <v>52</v>
       </c>
       <c r="I191" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="J191" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="K191" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="L191" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M191" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="N191" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="T191" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W191" t="s">
         <v>34</v>
@@ -11453,7 +11450,7 @@
         <v>72</v>
       </c>
       <c r="Z191" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="192" spans="1:27" x14ac:dyDescent="0.25">
@@ -11461,25 +11458,25 @@
         <v>79</v>
       </c>
       <c r="B192" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C192" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="D192" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="E192" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="F192" t="s">
         <v>52</v>
       </c>
       <c r="K192" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="L192" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="M192" t="s">
         <v>41</v>
@@ -11503,37 +11500,37 @@
         <v>80</v>
       </c>
       <c r="B193" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C193" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="D193" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E193" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="F193" t="s">
         <v>52</v>
       </c>
       <c r="J193" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="K193" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="L193" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M193" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N193" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T193" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W193" t="s">
         <v>34</v>
@@ -11545,7 +11542,7 @@
         <v>72</v>
       </c>
       <c r="Z193" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -11553,34 +11550,34 @@
         <v>81</v>
       </c>
       <c r="B194" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C194" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D194" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E194" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="F194" t="s">
         <v>52</v>
       </c>
       <c r="J194" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L194" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M194" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N194" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T194" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W194" t="s">
         <v>88</v>
@@ -11600,34 +11597,34 @@
         <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C195" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D195" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E195" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="F195" t="s">
         <v>52</v>
       </c>
       <c r="J195" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L195" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M195" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N195" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T195" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W195" t="s">
         <v>88</v>
@@ -11647,34 +11644,34 @@
         <v>83</v>
       </c>
       <c r="B196" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C196" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D196" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E196" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="F196" t="s">
         <v>52</v>
       </c>
       <c r="J196" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L196" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M196" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N196" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T196" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W196" t="s">
         <v>88</v>
@@ -11694,34 +11691,34 @@
         <v>84</v>
       </c>
       <c r="B197" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C197" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="D197" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E197" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="F197" t="s">
         <v>52</v>
       </c>
       <c r="J197" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L197" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M197" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N197" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T197" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W197" t="s">
         <v>88</v>
@@ -11741,34 +11738,34 @@
         <v>85</v>
       </c>
       <c r="B198" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C198" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="D198" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="E198" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="F198" t="s">
         <v>52</v>
       </c>
       <c r="J198" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L198" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M198" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N198" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T198" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W198" t="s">
         <v>88</v>
@@ -11788,34 +11785,34 @@
         <v>86</v>
       </c>
       <c r="B199" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C199" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D199" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E199" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="F199" t="s">
         <v>52</v>
       </c>
       <c r="J199" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L199" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M199" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N199" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T199" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W199" t="s">
         <v>88</v>
@@ -11835,34 +11832,34 @@
         <v>87</v>
       </c>
       <c r="B200" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C200" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D200" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E200" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="F200" t="s">
         <v>52</v>
       </c>
       <c r="J200" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L200" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M200" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N200" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T200" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W200" t="s">
         <v>88</v>
@@ -11882,34 +11879,34 @@
         <v>88</v>
       </c>
       <c r="B201" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C201" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D201" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E201" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="F201" t="s">
         <v>52</v>
       </c>
       <c r="J201" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L201" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M201" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N201" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T201" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W201" t="s">
         <v>88</v>
@@ -11929,34 +11926,34 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C202" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="D202" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="E202" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="F202" t="s">
         <v>52</v>
       </c>
       <c r="J202" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L202" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M202" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N202" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T202" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W202" t="s">
         <v>88</v>
@@ -11976,34 +11973,34 @@
         <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C203" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="D203" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="E203" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="F203" t="s">
         <v>52</v>
       </c>
       <c r="J203" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L203" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M203" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N203" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T203" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W203" t="s">
         <v>88</v>
@@ -12023,34 +12020,34 @@
         <v>91</v>
       </c>
       <c r="B204" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C204" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D204" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E204" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="F204" t="s">
         <v>52</v>
       </c>
       <c r="J204" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L204" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M204" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N204" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T204" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W204" t="s">
         <v>88</v>
@@ -12070,34 +12067,34 @@
         <v>92</v>
       </c>
       <c r="B205" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C205" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="D205" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E205" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="F205" t="s">
         <v>52</v>
       </c>
       <c r="J205" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L205" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M205" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N205" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T205" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W205" t="s">
         <v>88</v>
@@ -12117,34 +12114,34 @@
         <v>93</v>
       </c>
       <c r="B206" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C206" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="D206" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E206" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="F206" t="s">
         <v>52</v>
       </c>
       <c r="J206" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L206" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M206" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N206" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T206" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W206" t="s">
         <v>88</v>
@@ -12164,34 +12161,34 @@
         <v>94</v>
       </c>
       <c r="B207" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C207" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="D207" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="E207" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="F207" t="s">
         <v>52</v>
       </c>
       <c r="J207" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L207" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M207" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N207" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T207" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W207" t="s">
         <v>88</v>
@@ -12211,34 +12208,34 @@
         <v>95</v>
       </c>
       <c r="B208" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C208" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D208" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="E208" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="F208" t="s">
         <v>52</v>
       </c>
       <c r="J208" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L208" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M208" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N208" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T208" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W208" t="s">
         <v>88</v>
@@ -12258,34 +12255,34 @@
         <v>96</v>
       </c>
       <c r="B209" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C209" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D209" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E209" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="F209" t="s">
         <v>52</v>
       </c>
       <c r="J209" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L209" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M209" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N209" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T209" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W209" t="s">
         <v>88</v>
@@ -12305,34 +12302,34 @@
         <v>97</v>
       </c>
       <c r="B210" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C210" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="D210" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="E210" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="F210" t="s">
         <v>52</v>
       </c>
       <c r="J210" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L210" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M210" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N210" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T210" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W210" t="s">
         <v>88</v>
@@ -12352,34 +12349,34 @@
         <v>98</v>
       </c>
       <c r="B211" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C211" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D211" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="E211" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="F211" t="s">
         <v>52</v>
       </c>
       <c r="J211" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L211" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M211" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N211" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T211" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W211" t="s">
         <v>88</v>
@@ -12399,34 +12396,34 @@
         <v>99</v>
       </c>
       <c r="B212" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C212" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D212" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="E212" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="F212" t="s">
         <v>52</v>
       </c>
       <c r="J212" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="L212" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M212" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="N212" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="T212" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W212" t="s">
         <v>88</v>
@@ -12446,25 +12443,25 @@
         <v>100</v>
       </c>
       <c r="B213" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C213" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D213" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="E213" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="F213" t="s">
         <v>52</v>
       </c>
       <c r="J213" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="L213" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M213" t="s">
         <v>41</v>
@@ -12474,7 +12471,7 @@
         <v>88</v>
       </c>
       <c r="X213" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="Y213" t="s">
         <v>88</v>
@@ -12488,37 +12485,37 @@
         <v>101</v>
       </c>
       <c r="B214" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C214" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D214" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E214" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="F214" t="s">
         <v>52</v>
       </c>
       <c r="J214" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="L214" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M214" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="N214" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="T214" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="V214" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="W214" t="s">
         <v>34</v>
@@ -12530,7 +12527,7 @@
         <v>72</v>
       </c>
       <c r="Z214" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="215" spans="1:27" ht="90" x14ac:dyDescent="0.25">
@@ -12538,34 +12535,34 @@
         <v>102</v>
       </c>
       <c r="B215" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C215" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D215" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E215" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="F215" t="s">
         <v>52</v>
       </c>
       <c r="J215" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="L215" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M215" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="N215" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="T215" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="W215" t="s">
         <v>34</v>
@@ -12577,7 +12574,7 @@
         <v>72</v>
       </c>
       <c r="Z215" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="216" spans="1:27" x14ac:dyDescent="0.25">
@@ -12585,36 +12582,36 @@
         <v>103</v>
       </c>
       <c r="B216" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C216" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D216" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E216" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F216" t="s">
         <v>52</v>
       </c>
       <c r="J216" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="L216" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M216" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="T216" s="2"/>
       <c r="W216" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="Z216"/>
       <c r="AA216" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
     </row>
     <row r="217" spans="1:27" x14ac:dyDescent="0.25">
@@ -12622,28 +12619,28 @@
         <v>104</v>
       </c>
       <c r="B217" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C217" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D217" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="E217" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="F217" t="s">
         <v>52</v>
       </c>
       <c r="J217" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L217" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="T217" s="2"/>
       <c r="W217" t="s">
@@ -12656,10 +12653,10 @@
         <v>72</v>
       </c>
       <c r="Z217" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="AA217" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
     </row>
     <row r="218" spans="1:27" x14ac:dyDescent="0.25">
@@ -12667,25 +12664,25 @@
         <v>105</v>
       </c>
       <c r="B218" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C218" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D218" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="E218" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="F218" t="s">
         <v>52</v>
       </c>
       <c r="J218" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="L218" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M218" t="s">
         <v>41</v>
@@ -12709,22 +12706,22 @@
         <v>106</v>
       </c>
       <c r="B219" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C219" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D219" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E219" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="F219" t="s">
         <v>52</v>
       </c>
       <c r="J219" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="M219" t="s">
         <v>41</v>
@@ -12748,22 +12745,22 @@
         <v>107</v>
       </c>
       <c r="B220" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C220" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D220" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E220" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="F220" t="s">
         <v>52</v>
       </c>
       <c r="J220" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M220" t="s">
         <v>41</v>
@@ -12787,22 +12784,22 @@
         <v>108</v>
       </c>
       <c r="B221" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C221" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D221" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="E221" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="F221" t="s">
         <v>52</v>
       </c>
       <c r="J221" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="M221" t="s">
         <v>41</v>
@@ -12826,22 +12823,22 @@
         <v>109</v>
       </c>
       <c r="B222" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C222" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="D222" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E222" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="F222" t="s">
         <v>52</v>
       </c>
       <c r="J222" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="M222" t="s">
         <v>41</v>
@@ -12865,25 +12862,25 @@
         <v>110</v>
       </c>
       <c r="B223" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C223" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D223" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E223" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="F223" t="s">
         <v>52</v>
       </c>
       <c r="J223" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="K223" s="10" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="M223" t="s">
         <v>41</v>
@@ -12907,22 +12904,22 @@
         <v>111</v>
       </c>
       <c r="B224" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C224" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D224" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E224" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F224" t="s">
         <v>52</v>
       </c>
       <c r="J224" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M224" t="s">
         <v>41</v>
@@ -12946,22 +12943,22 @@
         <v>112</v>
       </c>
       <c r="B225" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C225" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D225" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E225" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="F225" t="s">
         <v>52</v>
       </c>
       <c r="J225" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="M225" t="s">
         <v>41</v>
